--- a/files_by_year/2021_randomsample.xlsx
+++ b/files_by_year/2021_randomsample.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +16,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +48,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,96 +429,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R67"/>
+  <dimension ref="A1:S65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>DOI</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Published Date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Embargo Release</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>File Count</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>File 1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>File 2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>File 3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>File 4</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>File 5</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>File 6</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>File 7</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>File 8</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>File 9</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>File 10</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>File 11</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>File 12</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>File 13</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
@@ -511,43 +532,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>h128nf42c</t>
+          <t>4j03d071p</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.18130/6g3e-q285</t>
+          <t>10.18130/y3sh-zj58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Scaglione_Austin_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-17</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scaglione_Austin_STS Research Paper.pdf</t>
+          <t>1_Spaeth_Joseph_2021_BS.pdf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scaglione_Austin_Sociotechnical Synthesis.pdf</t>
+          <t>2_Spaeth_Joseph_2021_BS.pdf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Scaglione_Austin_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>3_Spaeth_Joseph_2021_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4_Spaeth_Joseph_2021_BS.pdf</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -556,50 +577,51 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3197xm85r</t>
+          <t>37720d622</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.18130/xyj8-de58</t>
+          <t>10.18130/et8d-he52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1_Ningtyas_Adinda_2021_BS.pdf</t>
-        </is>
+          <t>2021-05-20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2_Ningtyas_Adinda_2021_BS.pdf</t>
+          <t>Rizvi_Saqib_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3_Ningtyas_Adinda_2021_BS.pdf</t>
+          <t>Rizvi_Saqib_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4_Ningtyas_Adinda_2021_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Rizvi_Saqib_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Rizvi_Saqib_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
@@ -608,50 +630,53 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rf55z835f</t>
+          <t>6m311p979</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.18130/2e84-qn87</t>
+          <t>10.18130/5k2x-t945</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2021-05-15</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Mendel_Benjamin_2021_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mendel_Benjamin_2021_STS Research Paper.pdf</t>
+          <t>Bharani_Nikhil_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mendel_Benjamin_2021_Sociotechnical Synthesis.pdf</t>
+          <t>Bharani_Nikhil_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Mendel_Benjamin_2021_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Bharani_Nikhil_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Bharani_Nikhil_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -660,50 +685,51 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>dr26xz41n</t>
+          <t>q237hs98v</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.18130/f9sc-4k58</t>
+          <t>10.18130/qwm9-6h85</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Faruqi_Rayaan_Prospectus.pdf</t>
-        </is>
+          <t>2021-12-12</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Faruqi_Rayaan_STS Research Paper.pdf</t>
+          <t>Choi_Emma_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Faruqi_Rayaan_Sociotechnical Synthesis.pdf</t>
+          <t>Choi_Emma_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Faruqi_Rayaan_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Choi_Emma_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Choi_Emma_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -712,19 +738,20 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jh343t173</t>
+          <t>pv63g1045</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10.18130/0f5y-7b62</t>
+          <t>10.18130/d8km-ck04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -732,30 +759,30 @@
           <t>2021-05-16</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1_Choi_Rachel_2021_BS.pdf</t>
-        </is>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2_Choi_Rachel_2021_BS.pdf</t>
+          <t>Toussaint_Claire_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3_Choi_Rachel_2021_BS.pdf</t>
+          <t>Toussaint_Claire_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4_Choi_Rachel_2021_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Toussaint_Claire_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Toussaint_Claire_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -764,19 +791,20 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>zs25x915k</t>
+          <t>5h73pw85g</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.18130/38sf-5x71</t>
+          <t>10.18130/6g7b-sc80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -784,30 +812,32 @@
           <t>2021-05-13</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Li_Beatrice_Prospectus.pdf</t>
-        </is>
+      <c r="D7" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Li_Beatrice_STS_Research_Paper.pdf</t>
+          <t>Wang_Andrew_Designing Secure and Usable Wake Words.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Li_Beatrice_Sociotechnical_Synthesis.pdf</t>
+          <t>Wang_Andrew_Propsectus.pdf</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Li_Beatrice_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Wang_Andrew_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Wang_Andrew_Understanding Why Users Cannot Affect the Smart Speaker Data Collection Design.pdf</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -816,19 +846,20 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2227mq38r</t>
+          <t>zk51vh537</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10.18130/0p45-0j24</t>
+          <t>10.18130/6kxg-xb23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -836,30 +867,30 @@
           <t>2021-05-10</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Prospectus.pdf</t>
-        </is>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sociotechnical Synthesis.pdf</t>
+          <t>Burtner_Sean_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>The Advancement and Shortcomings of Ethics in Clinical Research (STS Research Paper).pdf</t>
+          <t>Burtner_Sean_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>The Effect of Hornerin Knockdown on Tumor Vasculature in Melanoma (Technical Report).pdf</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Burtner_Sean_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Burtner_Sean_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
@@ -868,19 +899,20 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2j62s574v</t>
+          <t>qn59q482q</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.18130/s2mh-8486</t>
+          <t>10.18130/ee45-m908</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -888,30 +920,32 @@
           <t>2021-05-13</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Levy_Trent_Prospectus.pdf</t>
-        </is>
+      <c r="D9" s="2" t="n">
+        <v>44694</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Levy_Trent_STS Research Paper.pdf</t>
+          <t>Donnelly_Vienna_Developing a Recommendation System for Collegiate Golf Recruiting.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Levy_Trent_Sociotechnical Synthesis.pdf</t>
+          <t>Donnelly_Vienna_Prospectus.pdf</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Levy_Trent_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Donnelly_Vienna_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Donnelly_Vienna_The Impacts of Using AI-Backed Applicant Tracking Systems for Recruitment Practices.pdf</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -920,50 +954,51 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6m311p98k</t>
+          <t>3t945r59b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.18130/rdtf-ts97</t>
+          <t>10.18130/4jqv-k856</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ding_Sihan_Porspectus.pdf</t>
-        </is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ding_Sihan_STS Research Paper.pdf</t>
+          <t>Bailey_Cameron_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ding_Sihan_Sociotechnical Synthesis.pdf</t>
+          <t>Bailey_Cameron_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Ding_Sihan_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Bailey_Cameron_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Bailey_Cameron_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -972,50 +1007,51 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1z40kt628</t>
+          <t>qv33rx38g</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.18130/yxx4-3m35</t>
+          <t>10.18130/x1z3-t498</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Du_Danna_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Du_Danna_STS_Research_Paper.pdf</t>
+          <t>1_Myers_Landry_2021_BS.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Du_Danna_Sociotechnical_Synthesis.pdf</t>
+          <t>2_Myers_Landry_2021_BS.pdf</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Du_Danna_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>3_Myers_Landry_2021_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4_Myers_Landry_2021_BS.pdf</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1024,50 +1060,51 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bz60cw889</t>
+          <t>st74cr36j</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10.18130/qedh-6r97</t>
+          <t>10.18130/tw10-fd71</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Barlow_Vanessa_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barlow_Vanessa_STS Research Paper.pdf</t>
+          <t>Cao_Dylan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Barlow_Vanessa_Sociotechnical Synthesis.pdf</t>
+          <t>Cao_Dylan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Barlow_Vanessa_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Cao_Dylan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Cao_Dylan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1076,50 +1113,51 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3484zh71n</t>
+          <t>wp988k562</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10.18130/yamx-4t92</t>
+          <t>10.18130/jqv5-3s77</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Fitzgerald_Graham_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-06</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fitzgerald_Graham_STS Research Paper.pdf</t>
+          <t>Khan_Ahnaf_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fitzgerald_Graham_Sociotechnical Synthesis.pdf</t>
+          <t>Khan_Ahnaf_STS_Paper.pdf</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Fitzgerald_Graham_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Khan_Ahnaf_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Khan_Ahnaf_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
@@ -1128,50 +1166,51 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nv9353847</t>
+          <t>w0892b72m</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10.18130/k96b-k842</t>
+          <t>10.18130/dg0t-9e08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Barrett_David_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barrett_David_STS Research Paper.pdf</t>
+          <t>Cooper_John_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Barrett_David_Sociotechnical Synthesis.pdf</t>
+          <t>Cooper_John_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Barrett_David_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Cooper_John_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Cooper_John_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1180,50 +1219,51 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6395w787t</t>
+          <t>sf2685845</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10.18130/23p5-kq93</t>
+          <t>10.18130/esr2-qa18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Walker_Avery_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Walker_Avery_STS Research Paper.pdf</t>
+          <t>Henriques_Sydney_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Walker_Avery_Sociotechnical Synthesis.pdf</t>
+          <t>Henriques_Sydney_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Walker_Avery_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Henriques_Sydney_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Henriques_Sydney_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
@@ -1232,50 +1272,51 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2f75r8765</t>
+          <t>s1784m43w</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10.18130/tndr-xk57</t>
+          <t>10.18130/w1t9-bm48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Prospectus</t>
-        </is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>STS Research Paper</t>
+          <t>Rantas_Jacob_A User Interface Informing Medical Staff on Continuous Indoor Environmental Quality to  Support Patient Care and Airborne Disease Mitigation.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sociotechnical Synthesis</t>
+          <t>Rantas_Jacob_Creating “Smarter” Cities through Human Involvement.pdf</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Technical Report</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Rantas_Jacob_Prospectus.pdf</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Rantas_Jacob_Sociotechnical Sythesis.pdf</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1284,50 +1325,51 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>zs25x9149</t>
+          <t>kp78gh301</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10.18130/fqqd-fh38</t>
+          <t>10.18130/js3g-3627</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2021-05-18</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>4</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Gill_Sarah_2021_BS_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gill_Sarah_2021_BS_STS_Research_Paper.pdf</t>
+          <t>1_Stoloff_Eric_2021_BS.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gill_Sarah_2021_BS_Socio-Technical_Synthesis.pdf</t>
+          <t>2_Stoloff_Eric_2021_BS.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Gill_Sarah_2021_BS_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>3_Stoloff_Eric_2021_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4_Stoloff_Eric_2021_BS.pdf</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
@@ -1336,50 +1378,51 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>zc77sq851</t>
+          <t>2f75r8854</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10.18130/tcvw-xq24</t>
+          <t>10.18130/y8d3-v862</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1_Rothemich_Brian_2021_BS.pdf</t>
-        </is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2_Rothemich_Brian_2021_BS.pdf</t>
+          <t>Goldstein_Zachary_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3_Rothemich_Brian_2021_BS.pdf</t>
+          <t>Goldstein_Zachary_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4_Rothemich_Brian_2021_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Goldstein_Zachary_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Goldstein_Zachary_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1388,19 +1431,20 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3n203z86h</t>
+          <t>jq085k641</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10.18130/wb5k-gn26</t>
+          <t>10.18130/pnrf-cr16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1408,30 +1452,30 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Law_Noelle_Prospectus.pdf</t>
-        </is>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>4</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Law_Noelle_STS Research Paper.pdf</t>
+          <t>Jacobson_Nathan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Law_Noelle_Sociotechnical Synthesis.pdf</t>
+          <t>Jacobson_Nathan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Law_Noelle_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Jacobson_Nathan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Jacobson_Nathan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1440,50 +1484,51 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cz30pt443</t>
+          <t>41687j330</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10.18130/n0fj-r567</t>
+          <t>10.18130/6fts-xq88</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>4</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Maheshwari_Shubhi_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-06</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>4</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maheshwari_Shubhi_STS Research Paper.pdf</t>
+          <t>Shen_Edward_2021_BS_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Maheshwari_Shubhi_Sociotechnical Synthesis.pdf</t>
+          <t>Shen_Edward_2021_BS_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Maheshwari_Shubhi_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Shen_Edward_2021_BS_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Shen_Edward_2021_BS_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1492,50 +1537,51 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7m01bm36f</t>
+          <t>gm80hw197</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10.18130/v9b7-s165</t>
+          <t>10.18130/ezpt-0y02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Hickey_Caroline_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>4</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hickey_Caroline_STS Research Paper.pdf</t>
+          <t>Amelung_Connor_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hickey_Caroline_Sociotechnical Synthesis.pdf</t>
+          <t>Amelung_Connor_STS Research Project.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hickey_Caroline_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Amelung_Connor_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Amelung_Connor_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -1544,50 +1590,53 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2v23vv261</t>
+          <t>ms35t9448</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>10.18130/78z1-8w74</t>
+          <t>10.18130/n3ef-hc29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2021-05-09</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Moon_Nicholas_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Moon_Nicholas_STS_Research_Paper.pdf</t>
+          <t>Do_Nathan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moon_Nicholas_Sociotechnical Sythesis.pdf</t>
+          <t>Do_Nathan_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Moon_Nicholas_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>Do_Nathan_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Do_Nathan_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -1596,50 +1645,53 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>t435gf049</t>
+          <t>cc08hg65j</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>10.18130/t9zp-md26</t>
+          <t>10.18130/s178-xd78</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1_Reilly_Philip_2021_BS.pdf</t>
-        </is>
+          <t>2021-05-17</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2_Reilly_Philip_2021_BS.pdf</t>
+          <t>Reihani_Sean_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3_Reilly_Philip_2021_BS.pdf</t>
+          <t>Reihani_Sean_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4_Reilly_Philip_2021_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Reihani_Sean_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Reihani_Sean_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -1648,50 +1700,51 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>zk51vh537</t>
+          <t>9593tv88f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10.18130/6kxg-xb23</t>
+          <t>10.18130/xgsc-qb59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Burtner_Sean_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Burtner_Sean_STS Research Paper.pdf</t>
+          <t>Pincus_James_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Burtner_Sean_Sociotechnical Synthesis.pdf</t>
+          <t>Pincus_James_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Burtner_Sean_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>Pincus_James_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Pincus_James_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -1700,50 +1753,51 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vt150k145</t>
+          <t>h128nf62v</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10.18130/nd3h-hn68</t>
+          <t>10.18130/gtt4-c009</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Sonnakul_Thrishna_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-15</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sonnakul_Thrishna_STS Research Paper.pdf</t>
+          <t>Owen_Caleb_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sonnakul_Thrishna_Sociotechnical Synthesis.pdf</t>
+          <t>Owen_Caleb_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sonnakul_Thrishna_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Owen_Caleb_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Owen_Caleb_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -1752,50 +1806,53 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>j098zc06b</t>
+          <t>d504rm081</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10.18130/bjvn-ng03</t>
+          <t>10.18130/cjdd-q308</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Sprouse_Noah_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sprouse_Noah_STS_Research Paper.pdf</t>
+          <t>Wu_Arthur_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sprouse_Noah_Sociotechnical Synthesis.pdf</t>
+          <t>Wu_Arthur_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Sprouse_Noah_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Wu_Arthur_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Wu_Arthur_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
@@ -1804,50 +1861,51 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="n">
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>t148fh99d</t>
+          <t>6h440t24r</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10.18130/8rr7-j670</t>
+          <t>10.18130/wazx-4f28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>4</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>STS Research Paper.pdf</t>
+          <t>Masters_Nathaniel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sociotechnical Synthesis.pdf</t>
+          <t>Masters_Nathaniel_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>Masters_Nathaniel_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Masters_Nathaniel_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
@@ -1856,50 +1914,51 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>js956g583</t>
+          <t>1v53jx96v</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10.18130/1dkz-p843</t>
+          <t>10.18130/fw6c-sd87</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Roe_Bailey_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>4</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Roe_Bailey_STS Research Paper.pdf</t>
+          <t>Santos_Joshua_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Roe_Bailey_Sociotechnical Synthesis.pdf</t>
+          <t>Santos_Joshua_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Roe_Bailey_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>Santos_Joshua_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Santos_Joshua_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -1908,19 +1967,20 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2n49t239s</t>
+          <t>bg257f68r</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10.18130/z468-e612</t>
+          <t>10.18130/b545-ab39</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1928,30 +1988,30 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="D29" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Fishbein_John_Prospectus.pdf</t>
-        </is>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>4</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fishbein_John_STS Research Paper.pdf</t>
+          <t>Prospectus</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fishbein_John_Sociotechnical Synthesis.pdf</t>
+          <t>STS Research Paper</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Fishbein_John_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>Sociotechnical Synthesis</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Technical Report</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -1960,19 +2020,20 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>z029p551c</t>
+          <t>0g354g08r</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10.18130/359c-bn68</t>
+          <t>10.18130/21s9-db61</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1980,30 +2041,32 @@
           <t>2021-05-10</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Mann_Adam_Prospectus.pdf</t>
-        </is>
+      <c r="D30" s="2" t="n">
+        <v>45056</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mann_Adam_STS Research Paper.pdf</t>
+          <t>Albini_Tony_3D_Lung_Volume_Calculation_for_Scoliosis_Patients.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mann_Adam_Sociotechnical Synthesis.pdf</t>
+          <t>Albini_Tony_Fear_of_Genetic_Discrimination.pdf</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Mann_Adam_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Albini_Tony_Prospectus.pdf</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Albini_Tony_Sociotechnical_Summary.pdf</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2012,50 +2075,51 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05741s56d</t>
+          <t>h702q7192</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10.18130/70f1-hr54</t>
+          <t>10.18130/zadb-zx35</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>1_Yocom_Jack_2021_BS.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2_Yocom_Jack_2021_BS.pdf</t>
+          <t>Schlomer_Read_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3_Yocom_Jack_2021_BS.pdf</t>
+          <t>Schlomer_Read_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4_Yocom_Jack_2021_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Schlomer_Read_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Schlomer_Read_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2064,50 +2128,51 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ns064696t</t>
+          <t>x346d513j</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>10.18130/dyg0-9n58</t>
+          <t>10.18130/s6nf-s324</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Palugod_Lerene-Jade_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>4</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Palugod_Lerene-Jade_STS_Research_Paper.pdf</t>
+          <t>1_Hume_Christopher_2021_BS.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Palugod_Lerene-Jade_Sociotechnical_Synthesis.pdf</t>
+          <t>2_Hume_Christopher_2021_BS.pdf</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Palugod_Lerene-Jade_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>3_Hume_Christopher_2021_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4_Hume_Christopher_2021_BS.pdf</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -2116,19 +2181,20 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>c821gk55s</t>
+          <t>6969z157v</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>10.18130/zq1v-ve94</t>
+          <t>10.18130/ha4r-g244</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2136,30 +2202,30 @@
           <t>2021-05-14</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Schulte_Justine_Prospectus.pdf</t>
-        </is>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>4</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Schulte_Justine_STS Research Paper.pdf</t>
+          <t>Posey_Isabella_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Schulte_Justine_Sociotechnical Synthesis.pdf</t>
+          <t>Posey_Isabella_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schulte_Justine_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>Posey_Isabella_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Posey_Isabella_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2168,50 +2234,53 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="n">
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>d217qq202</t>
+          <t>qn59q4805</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10.18130/x4tz-1m15</t>
+          <t>10.18130/eejb-aa70</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>ProseCraig_Kayla_STS_Research_Paper.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>44510</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ProseCraig_Kayla_Sociotechnical_Synthesis.pdf</t>
+          <t>Lemley_Chase_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ProseCraig_Kayla_Technical_Report.pdf</t>
+          <t>Lemley_Chase_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>ProseCraig_Kayla_Thesis_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Lemley_Chase_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Lemley_Chase_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2220,50 +2289,53 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>n870zr590</t>
+          <t>gq67jr918</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10.18130/34pa-m117</t>
+          <t>10.18130/7jve-xz09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2021-05-15</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Luthar_Sonali_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>45059</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luthar_Sonali_STS Research Paper.pdf</t>
+          <t>Thran_Bailey_Behind_The_Meter_Implementing_Distributed_Energy_Technologies_To_Balance_Energy_Load_In_Virginia.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Luthar_Sonali_Sociotechnical Synthesis.pdf</t>
+          <t>Thran_Bailey_Buying_A_Green_Conscience_The_Development_And_Stabilization_Of_Carbon_Offsets.pdf</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Luthar_Sonali_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>Thran_Bailey_Prospectus.pdf</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Thran_Bailey_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -2272,50 +2344,53 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="n">
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0z708x25g</t>
+          <t>zp38wd37c</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10.18130/bv2q-1j81</t>
+          <t>10.18130/ae4x-3c47</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2021-05-20</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Eriksson_Clark_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>45061</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eriksson_Clark_STS Research Paper.pdf</t>
+          <t>Meng_Sarah_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Eriksson_Clark_Sociotechnical Synthesis.pdf</t>
+          <t>Meng_Sarah_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Eriksson_Clark_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Meng_Sarah_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Meng_Sarah_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
@@ -2324,50 +2399,51 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>j098zc08w</t>
+          <t>4f16c354s</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10.18130/8pmq-k615</t>
+          <t>10.18130/gw98-q649</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Wendelken_Craig_Improving Wind Turbine Efficiency Through Blade Design.pdf</t>
-        </is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>4</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wendelken_Craig_Prospectus.pdf</t>
+          <t>Landsman_Zackary_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Wendelken_Craig_Sociotechnical Synthesis.pdf</t>
+          <t>Landsman_Zackary_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Wendelken_Craig_Technological Innovation of Rideshare Electric Scooters as a Response to Increased Regulation.pdf</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>Landsman_Zackary_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Landsman_Zackary_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -2376,50 +2452,51 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8p58pd81d</t>
+          <t>9z9030672</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10.18130/40m2-s515</t>
+          <t>10.18130/ahk4-2y45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Liu_Jelena_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>4</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liu_Jelena_STS Research Paper.pdf</t>
+          <t>1_Lund_Bradley_2021_BS.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Liu_Jelena_Sociotechnical Synthesis.pdf</t>
+          <t>2_Lund_Bradley_2021_BS.pdf</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Liu_Jelena_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>3_Lund_Bradley_2021_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4_Lund_Bradley_2021_BS.pdf</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
@@ -2428,50 +2505,51 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="n">
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cj82k8048</t>
+          <t>3x816n53x</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10.18130/8p2f-8831</t>
+          <t>10.18130/8wxc-f928</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Glatz_Sarah_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-17</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>4</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Glatz_Sarah_STS_Research_Paper.pdf</t>
+          <t>Quach_Henry_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Glatz_Sarah_Sociotechnical_Synthesis</t>
+          <t>Quach_Henry_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Glatz_Sarah_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Quach_Henry_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Quach_Henry_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -2480,19 +2558,20 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="n">
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dz010q87p</t>
+          <t>qf85nc10x</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10.18130/30xn-rf05</t>
+          <t>10.18130/svpe-2c06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2500,30 +2579,30 @@
           <t>2021-05-14</t>
         </is>
       </c>
-      <c r="D40" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Staten_Ethan_Prospectus.pdf</t>
-        </is>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Staten_Ethan_STS Research Paper.pdf</t>
+          <t>Brewer_Alec_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Staten_Ethan_Sociotechnical Synthesis.pdf</t>
+          <t>Brewer_Alec_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Staten_Ethan_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Brewer_Alec_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Brewer_Alec_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
@@ -2532,50 +2611,51 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vq27zp305</t>
+          <t>zc77sq851</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10.18130/1gnz-2c65</t>
+          <t>10.18130/tcvw-xq24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Sana_Anoop_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sana_Anoop_STS Research Paper.pdf</t>
+          <t>1_Rothemich_Brian_2021_BS.pdf</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sana_Anoop_Sociotechnical Synthesis.pdf</t>
+          <t>2_Rothemich_Brian_2021_BS.pdf</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sana_Anoop_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>3_Rothemich_Brian_2021_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>4_Rothemich_Brian_2021_BS.pdf</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
@@ -2584,50 +2664,51 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>js956g57t</t>
+          <t>7m01bm398</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>10.18130/4rkj-jq77</t>
+          <t>10.18130/rrz7-1f15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Fedroff_Emily_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fedroff_Emily_STS Research Paper.pdf</t>
+          <t>Giraudeau_Luke_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fedroff_Emily_Sociotechnical Synthesis.pdf</t>
+          <t>Giraudeau_Luke_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Fedroff_Emily_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Giraudeau_Luke_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Giraudeau_Luke_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -2636,50 +2717,51 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>kd17ct49s</t>
+          <t>zs25x9149</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10.18130/dt6p-jt94</t>
+          <t>10.18130/fqqd-fh38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Prospectus</t>
-        </is>
+          <t>2021-05-18</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>STS Research Paper</t>
+          <t>Gill_Sarah_2021_BS_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sociotechnical Synthesis</t>
+          <t>Gill_Sarah_2021_BS_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Technical Report</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Gill_Sarah_2021_BS_Socio-Technical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Gill_Sarah_2021_BS_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -2688,19 +2770,20 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="n">
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4m90dw232</t>
+          <t>79407z122</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10.18130/jjps-vh03</t>
+          <t>10.18130/15tt-n428</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2708,30 +2791,30 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Kim_Josh_Prospectus.pdf</t>
-        </is>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>4</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kim_Josh_STS_Research_Paper.pdf</t>
+          <t>Trans_Sarah_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Kim_Josh_Sociotechnical_Synthesis.pdf</t>
+          <t>Trans_Sarah_STSResearchPaper.pdf</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Kim_Josh_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Trans_Sarah_SociotechnicalSynthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Trans_Sarah_TechnicalReport.pdf</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -2740,50 +2823,51 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="n">
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>w9505143w</t>
+          <t>q524jp50x</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10.18130/5nxg-kf56</t>
+          <t>10.18130/74zz-m135</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Griffin_Alex_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-09</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Griffin_Alex_STS_Research_Paper.pdf</t>
+          <t>Judge_Mary_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Griffin_Alex_Sociotechnical_Synthesis.pdf</t>
+          <t>Judge_Mary_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Griffin_Alex_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Judge_Mary_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Judge_Mary_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
@@ -2792,50 +2876,51 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="n">
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>41687j526</t>
+          <t>v405sb103</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10.18130/7ts3-2n87</t>
+          <t>10.18130/wggt-5806</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2021-12-15</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Kellas_Charles_Prospectus.pdf.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>4</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kellas_Charles_STS_Research_Paper.pdf</t>
+          <t>Hunter_Nathan_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Kellas_Charles_Sociotechnical_Synthesis.pdf</t>
+          <t>Hunter_Nathan_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kellas_Charles_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Hunter_Nathan_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Hunter_Nathan_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
@@ -2844,50 +2929,51 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>t435gd96t</t>
+          <t>9880vr775</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10.18130/wrtx-zx73</t>
+          <t>10.18130/syae-7e79</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Mahmood_Abdullah_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>4</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mahmood_Abdullah_STS Research Paper.pdf</t>
+          <t>Lenox_Adam_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Mahmood_Abdullah_Sociotechnical Synthesis.pdf</t>
+          <t>Lenox_Adam_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Mahmood_Abdullah_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Lenox_Adam_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Lenox_Adam_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
@@ -2896,50 +2982,51 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="n">
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>w0892b72m</t>
+          <t>hm50ts472</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10.18130/dg0t-9e08</t>
+          <t>10.18130/9yts-zr29</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Cooper_John_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>4</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cooper_John_STS_Research_Paper.pdf</t>
+          <t>Yi_Steven_2021_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cooper_John_Sociotechnical_Synthesis.pdf</t>
+          <t>Yi_Steven_2021_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Cooper_John_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Yi_Steven_2021_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Yi_Steven_2021_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
@@ -2948,50 +3035,53 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qn59q488c</t>
+          <t>pk02cb445</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10.18130/78h9-m834</t>
+          <t>10.18130/wswc-q183</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>1_Weis_Lauren_2021_BS.pdf</t>
-        </is>
+          <t>2021-05-09</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2_Weis_Lauren_2021_BS.pdf</t>
+          <t>Hung_Claire_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3_Weis_Lauren_2021_BS.pdf</t>
+          <t>Hung_Claire_STS_Research Paper.pdf</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4_Weis_Lauren_2021_BS.pdf</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Hung_Claire_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Hung_Claire_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
@@ -3000,19 +3090,20 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="n">
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>dr26xz372</t>
+          <t>47429996j</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>10.18130/1jx9-nf58</t>
+          <t>10.18130/r2d0-2w50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3020,30 +3111,32 @@
           <t>2021-05-12</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Limpic_Kyle_Prospectus.pdf</t>
-        </is>
+      <c r="D50" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="E50" t="n">
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Limpic_Kyle_STS Research Paper.pdf</t>
+          <t>Feaser_Forrest_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Limpic_Kyle_Sociotechnical Synthesis.pdf</t>
+          <t>Feaser_Forrest_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Limpic_Kyle_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Feaser_Forrest_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Feaser_Forrest_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
@@ -3052,50 +3145,51 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="n">
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>xk81jm04n</t>
+          <t>hm50ts55r</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>10.18130/cnsm-n154</t>
+          <t>10.18130/jg7p-a137</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Gagliostro_Andrew_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-16</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gagliostro_Andrew_STS Research Paper.pdf</t>
+          <t>Simmons_Gabriel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gagliostro_Andrew_Sociotechnical Synthesis.pdf</t>
+          <t>Simmons_Gabriel_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Gagliostro_Andrew_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Simmons_Gabriel_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Simmons_Gabriel_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
@@ -3104,50 +3198,51 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>02870w68z</t>
+          <t>v118rf424</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>10.18130/bq7n-dc98</t>
+          <t>10.18130/exsr-st76</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Gunderson_William_Integrating Modularity for Mass Customization of IoT Wireless Sensor Systems.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>4</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gunderson_William_Prospectus.pdf</t>
+          <t>1_Samaritano_Maria_2021_BS.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gunderson_William_Sociotechnical Synthesis.pdf</t>
+          <t>2_Samaritano_Maria_2021_BS.pdf</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Gunderson_William_The Impact of Specialty Coffee on Colombia's Coffee Industry.pdf</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>3_Samaritano_Maria_2021_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4_Samaritano_Maria_2021_BS.pdf</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
@@ -3156,50 +3251,53 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>x920fx687</t>
+          <t>xg94hq53b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10.18130/n9dz-9p50</t>
+          <t>10.18130/jw3k-tp44</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Walsh_Matthew_Capstone.pdf</t>
-        </is>
+          <t>2021-05-17</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="E53" t="n">
+        <v>4</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Walsh_Matthew_Prospectus.pdf</t>
+          <t>Render_Elayna_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Walsh_Matthew_STS_Research.pdf</t>
+          <t>Render_Elayna_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Walsh_Matthew_Sociotechnical_Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Render_Elayna_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Render_Elayna_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -3208,50 +3306,51 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5d86p108h</t>
+          <t>9p290b14j</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>10.18130/bd1c-0w90</t>
+          <t>10.18130/qazm-4s68</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Gibson_James_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>4</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gibson_James_STS Research Paper.pdf</t>
+          <t>Cartier_Mac_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gibson_James_Sociotechnical Synthesis.pdf</t>
+          <t>Cartier_Mac_STS_Research Paper.pdf</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Gibson_James_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Cartier_Mac_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Cartier_Mac_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -3260,50 +3359,53 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>f4752h309</t>
+          <t>0g354g091</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>10.18130/tbs5-r038</t>
+          <t>10.18130/z85m-6086</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Helmus_Daniel_MAE 4620 Final Report Autonomous Robot Team.pdf</t>
-        </is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>44512</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Helmus_Daniel_Prospectus.pdf</t>
+          <t>Woessner_Emma_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Helmus_Daniel_Sociotechnical Synthesis.pdf</t>
+          <t>Woessner_Emma_Single_Use_Syringes_The_Global_Impact_of_this_Technology_and_Why_It_May_Not_Be_Suitable_For_Everyone.pdf</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Helmus_Daniel_The Integration of Robotics in Society, Starting With Healthcare.pdf</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>Woessner_Emma_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Woessner_Emma_The_Development_of_a_One_Handed_Knee_Aspiration_Mechanism_to_Aid_in_Arthrocentesis.pdf</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -3312,50 +3414,51 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="n">
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>9k41zf32t</t>
+          <t>hh63sw636</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>10.18130/vnx6-m496</t>
+          <t>10.18130/2nwd-xd98</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2021-05-06</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Prospectus</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>STS Research Paper</t>
+          <t>Marcus_Adam_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sociotechnical Synthesis</t>
+          <t>Marcus_Adam_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Technical Report</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Marcus_Adam_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Marcus_Adam_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -3364,50 +3467,51 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="n">
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nv935383z</t>
+          <t>vh53ww43g</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>10.18130/8cgb-vw22</t>
+          <t>10.18130/5afd-w717</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Sharma_Anisha_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-06</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sharma_Anisha_STS Research Paper.pdf</t>
+          <t>Young_Brandie_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sharma_Anisha_Sociotechnical Synthesis.pdf</t>
+          <t>Young_Brandie_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sharma_Anisha_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Young_Brandie_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Young_Brandie_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
@@ -3416,50 +3520,51 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="n">
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>9p290b08d</t>
+          <t>2n49t2466</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10.18130/gh3x-1g58</t>
+          <t>10.18130/4dgw-hg65</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Koch_Andrew_Actor Network Theory Analysis of the United States Government Weapons Program.pdf</t>
-        </is>
+          <t>2021-05-15</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Koch_Andrew_Prospectus.pdf</t>
+          <t>Ehler_Caroline_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Koch_Andrew_Sociotechnical Synthesis.pdf</t>
+          <t>Ehler_Caroline_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Koch_Andrew_Trust and Security of Embedded Smart Devices in Advanced Logistics Systems.pdf</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Ehler_Caroline_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Ehler_Caroline_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -3468,50 +3573,53 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>d217qq14x</t>
+          <t>8p58pd86s</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10.18130/jy52-a107</t>
+          <t>10.18130/dq9a-3x96</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2021-05-12</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Latvis_Cole_Design of a Microfluidics Device for Facile Processing of Encapsulated Stem Cells.pdf</t>
-        </is>
+          <t>2021-05-14</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>45060</v>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Latvis_Cole_Insights for Responsible and Rapid Adoption of Emerging Medical Technologies.pdf</t>
+          <t>Wettstone_Erin_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Latvis_Cole_Prospectus.pdf</t>
+          <t>Wettstone_Erin_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Latvis_Cole_Sociotechnical_Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Wettstone_Erin_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Wettstone_Erin_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -3520,50 +3628,51 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>zg64tm815</t>
+          <t>hh63sw58b</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10.18130/1fax-p063</t>
+          <t>10.18130/s82f-3r41</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2021-05-17</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1_Ghany_Brandon_Sociotechnical_Synthesis.pdf</t>
-        </is>
+          <t>2021-05-10</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>4</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2_Ghany_Brandon_Technical_Report.pdf</t>
+          <t>Thomas_Jeremiah_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3_Ghany_Brandon_STS_Research_Paper.pdf</t>
+          <t>Thomas_Jeremiah_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4_Ghany_Brandon_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>Thomas_Jeremiah_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Thomas_Jeremiah_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -3572,50 +3681,51 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="n">
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6d56zx53t</t>
+          <t>mw22v6348</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10.18130/ze25-9q46</t>
+          <t>10.18130/wb4y-1z85</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2021-05-10</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>1_Anton_Helen_2021_BS_Sociotechnical Synthesis.pdf</t>
-        </is>
+          <t>2021-05-05</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>4</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2_Anton_Helen_2021_BS_Technical Report.pdf</t>
+          <t>Chappidi_Soumya_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>3_Anton_Helen_2021_BS_STS Research Paper.pdf</t>
+          <t>Chappidi_Soumya_STS_Research_Paper.pdf</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4_Anton_Helen_2021_BS_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>Chappidi_Soumya_Sociotechnical_Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Chappidi_Soumya_Technical_Report.pdf</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
@@ -3624,50 +3734,53 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0z708x23x</t>
+          <t>r494vk98q</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10.18130/xv99-pn34</t>
+          <t>10.18130/y2zc-xm38</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2021-05-11</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Schach_Samuel_3D LUNG VOLUME CALCULATION FOR SCOLIOSIS.pdf</t>
-        </is>
+          <t>2021-05-15</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Schach_Samuel_BARRIERS TO HEALTHCARE FOR THE MARSHALLESE IN NORTHWEST ARKANSAS.pdf</t>
+          <t>Kodama_William_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Schach_Samuel_Prospectus.pdf</t>
+          <t>Kodama_William_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schach_Samuel_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>Kodama_William_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Kodama_William_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
@@ -3676,50 +3789,53 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>xd07gt51k</t>
+          <t>1v53jx95k</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>10.18130/e8r1-7791</t>
+          <t>10.18130/1y8d-ch82</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2021-05-14</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Marquis_Caroline_ConfrontingtheWaterEthicsofaDominantSociety.pdf</t>
-        </is>
+          <t>2021-05-12</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>44513</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Marquis_Caroline_MeadowCreekWaterManagementPlan.pdf</t>
+          <t>1_Wang_Yifan_2021_BS.pdf</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Marquis_Caroline_Prospectus.pdf</t>
+          <t>2_Wang_Yifan_2021_BS.pdf</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Marquis_Caroline_SociotechnicalSynthesis.pdf</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>3_Wang_Yifan_2021_BS.pdf</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>4_Wang_Yifan_2021_BS.pdf</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
@@ -3728,50 +3844,51 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="n">
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>h128nf62v</t>
+          <t>4f16c3616</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>10.18130/gtt4-c009</t>
+          <t>10.18130/jjn8-yg90</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2021-05-15</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Owen_Caleb_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>4</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Owen_Caleb_STS Research Paper.pdf</t>
+          <t>McBroom_Samuel_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Owen_Caleb_Sociotechnical Synthesis.pdf</t>
+          <t>McBroom_Samuel_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Owen_Caleb_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>McBroom_Samuel_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>McBroom_Samuel_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
@@ -3780,50 +3897,51 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="n">
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>9g54xj42t</t>
+          <t>dn39x241k</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10.18130/m6gw-6x43</t>
+          <t>10.18130/7cnh-1148</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2021-05-09</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Zoeller_Patrick_Prospectus.pdf</t>
-        </is>
+          <t>2021-05-13</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zoeller_Patrick_STS_Research_Paper.pdf</t>
+          <t>Peters_Thomas_Prospectus.pdf</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Zoeller_Patrick_Sociotechnical_Synthesis.pdf</t>
+          <t>Peters_Thomas_STS Research Paper.pdf</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Zoeller_Patrick_Technical_Report.pdf</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Peters_Thomas_Sociotechnical Synthesis.pdf</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Peters_Thomas_Technical Report.pdf</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -3832,111 +3950,8 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="n">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>8g84mn07k</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>10.18130/sefp-az69</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Fogarty_Katherine_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Fogarty_Katherine_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Fogarty_Katherine_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Fogarty_Katherine_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>1r66j1904</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>10.18130/81dj-f839</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2021-05-15</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Feeley_Brendan_Prospectus.pdf</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Feeley_Brendan_STS Research Paper.pdf</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Feeley_Brendan_Sociotechnical Synthesis.pdf</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Feeley_Brendan_Technical Report.pdf</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="n">
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
         <v>2021</v>
       </c>
     </row>
